--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122842182</v>
+        <v>122842019</v>
       </c>
       <c r="B2" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>361303</v>
+        <v>361324</v>
       </c>
       <c r="R2" t="n">
-        <v>6631185</v>
+        <v>6631171</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
         <v>122840408</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122841433</v>
+        <v>122842182</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>361325</v>
+        <v>361303</v>
       </c>
       <c r="R4" t="n">
-        <v>6631198</v>
+        <v>6631185</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122841777</v>
+        <v>122840738</v>
       </c>
       <c r="B5" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>361311</v>
+        <v>361349</v>
       </c>
       <c r="R5" t="n">
-        <v>6631219</v>
+        <v>6631211</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122842508</v>
+        <v>122841433</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>361294</v>
+        <v>361325</v>
       </c>
       <c r="R6" t="n">
-        <v>6631130</v>
+        <v>6631198</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,7 +1274,7 @@
         <v>122841555</v>
       </c>
       <c r="B7" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122842019</v>
+        <v>122841777</v>
       </c>
       <c r="B8" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>361324</v>
+        <v>361311</v>
       </c>
       <c r="R8" t="n">
-        <v>6631171</v>
+        <v>6631219</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,10 +1513,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122840608</v>
+        <v>122842508</v>
       </c>
       <c r="B9" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1562,13 +1562,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>361349</v>
+        <v>361294</v>
       </c>
       <c r="R9" t="n">
-        <v>6631211</v>
+        <v>6631130</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122842019</v>
+        <v>122842182</v>
       </c>
       <c r="B2" t="n">
         <v>98355</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>361324</v>
+        <v>361303</v>
       </c>
       <c r="R2" t="n">
-        <v>6631171</v>
+        <v>6631185</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122840408</v>
+        <v>122841555</v>
       </c>
       <c r="B3" t="n">
         <v>98355</v>
@@ -829,20 +829,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>361347</v>
+        <v>361315</v>
       </c>
       <c r="R3" t="n">
-        <v>6631224</v>
+        <v>6631258</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122842182</v>
+        <v>122841433</v>
       </c>
       <c r="B4" t="n">
         <v>98355</v>
@@ -943,7 +952,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>361303</v>
+        <v>361325</v>
       </c>
       <c r="R4" t="n">
-        <v>6631185</v>
+        <v>6631198</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122840738</v>
+        <v>122842508</v>
       </c>
       <c r="B5" t="n">
         <v>98355</v>
@@ -1064,7 +1073,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1078,13 +1087,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>361349</v>
+        <v>361294</v>
       </c>
       <c r="R5" t="n">
-        <v>6631211</v>
+        <v>6631130</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,7 +1159,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122841433</v>
+        <v>122842019</v>
       </c>
       <c r="B6" t="n">
         <v>98355</v>
@@ -1185,7 +1194,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1199,13 +1208,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>361325</v>
+        <v>361324</v>
       </c>
       <c r="R6" t="n">
-        <v>6631198</v>
+        <v>6631171</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122841555</v>
+        <v>122840608</v>
       </c>
       <c r="B7" t="n">
         <v>98355</v>
@@ -1306,7 +1315,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1320,13 +1329,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>361315</v>
+        <v>361349</v>
       </c>
       <c r="R7" t="n">
-        <v>6631258</v>
+        <v>6631211</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1355,7 +1364,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1374,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,7 +1401,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122841777</v>
+        <v>122840408</v>
       </c>
       <c r="B8" t="n">
         <v>98355</v>
@@ -1425,26 +1434,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>361311</v>
+        <v>361347</v>
       </c>
       <c r="R8" t="n">
-        <v>6631219</v>
+        <v>6631224</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,7 +1513,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122842508</v>
+        <v>122841777</v>
       </c>
       <c r="B9" t="n">
         <v>98355</v>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1562,13 +1562,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>361294</v>
+        <v>361311</v>
       </c>
       <c r="R9" t="n">
-        <v>6631130</v>
+        <v>6631219</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122842182</v>
+        <v>122840608</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>361303</v>
+        <v>361349</v>
       </c>
       <c r="R2" t="n">
-        <v>6631185</v>
+        <v>6631211</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122841555</v>
+        <v>122842182</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>361315</v>
+        <v>361303</v>
       </c>
       <c r="R3" t="n">
-        <v>6631258</v>
+        <v>6631185</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122841433</v>
+        <v>122842508</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>361325</v>
+        <v>361294</v>
       </c>
       <c r="R4" t="n">
-        <v>6631198</v>
+        <v>6631130</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122842508</v>
+        <v>122841433</v>
       </c>
       <c r="B5" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>361294</v>
+        <v>361325</v>
       </c>
       <c r="R5" t="n">
-        <v>6631130</v>
+        <v>6631198</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122842019</v>
+        <v>122841777</v>
       </c>
       <c r="B6" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>361324</v>
+        <v>361311</v>
       </c>
       <c r="R6" t="n">
-        <v>6631171</v>
+        <v>6631219</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122840608</v>
+        <v>122841555</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1329,13 +1329,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>361349</v>
+        <v>361315</v>
       </c>
       <c r="R7" t="n">
-        <v>6631211</v>
+        <v>6631258</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,7 +1404,7 @@
         <v>122840408</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122841777</v>
+        <v>122842019</v>
       </c>
       <c r="B9" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>361311</v>
+        <v>361324</v>
       </c>
       <c r="R9" t="n">
-        <v>6631219</v>
+        <v>6631171</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122842182</v>
+        <v>122842508</v>
       </c>
       <c r="B3" t="n">
         <v>98357</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>361303</v>
+        <v>361294</v>
       </c>
       <c r="R3" t="n">
-        <v>6631185</v>
+        <v>6631130</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122842508</v>
+        <v>122842182</v>
       </c>
       <c r="B4" t="n">
         <v>98357</v>
@@ -952,7 +952,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>361294</v>
+        <v>361303</v>
       </c>
       <c r="R4" t="n">
-        <v>6631130</v>
+        <v>6631185</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122840608</v>
+        <v>122841433</v>
       </c>
       <c r="B2" t="n">
         <v>98357</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>361349</v>
+        <v>361325</v>
       </c>
       <c r="R2" t="n">
-        <v>6631211</v>
+        <v>6631198</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122842508</v>
+        <v>122840408</v>
       </c>
       <c r="B3" t="n">
         <v>98357</v>
@@ -829,29 +829,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>361294</v>
+        <v>361347</v>
       </c>
       <c r="R3" t="n">
-        <v>6631130</v>
+        <v>6631224</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122842182</v>
+        <v>122842508</v>
       </c>
       <c r="B4" t="n">
         <v>98357</v>
@@ -952,7 +943,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -966,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>361303</v>
+        <v>361294</v>
       </c>
       <c r="R4" t="n">
-        <v>6631185</v>
+        <v>6631130</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122841433</v>
+        <v>122841777</v>
       </c>
       <c r="B5" t="n">
         <v>98357</v>
@@ -1073,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,13 +1078,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>361325</v>
+        <v>361311</v>
       </c>
       <c r="R5" t="n">
-        <v>6631198</v>
+        <v>6631219</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1150,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122841777</v>
+        <v>122840738</v>
       </c>
       <c r="B6" t="n">
         <v>98357</v>
@@ -1194,7 +1185,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1208,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>361311</v>
+        <v>361349</v>
       </c>
       <c r="R6" t="n">
-        <v>6631219</v>
+        <v>6631211</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1243,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,7 +1271,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122841555</v>
+        <v>122842019</v>
       </c>
       <c r="B7" t="n">
         <v>98357</v>
@@ -1315,7 +1306,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1329,13 +1320,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>361315</v>
+        <v>361324</v>
       </c>
       <c r="R7" t="n">
-        <v>6631258</v>
+        <v>6631171</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1374,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,7 +1392,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122840408</v>
+        <v>122842182</v>
       </c>
       <c r="B8" t="n">
         <v>98357</v>
@@ -1434,20 +1425,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>361347</v>
+        <v>361303</v>
       </c>
       <c r="R8" t="n">
-        <v>6631224</v>
+        <v>6631185</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,7 +1513,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122842019</v>
+        <v>122841555</v>
       </c>
       <c r="B9" t="n">
         <v>98357</v>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1562,13 +1562,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>361324</v>
+        <v>361315</v>
       </c>
       <c r="R9" t="n">
-        <v>6631171</v>
+        <v>6631258</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122841433</v>
+        <v>122840608</v>
       </c>
       <c r="B2" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>361325</v>
+        <v>361349</v>
       </c>
       <c r="R2" t="n">
-        <v>6631198</v>
+        <v>6631211</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
         <v>122840408</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122842508</v>
+        <v>122841433</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>361294</v>
+        <v>361325</v>
       </c>
       <c r="R4" t="n">
-        <v>6631130</v>
+        <v>6631198</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122841777</v>
+        <v>122842019</v>
       </c>
       <c r="B5" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>361311</v>
+        <v>361324</v>
       </c>
       <c r="R5" t="n">
-        <v>6631219</v>
+        <v>6631171</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122840738</v>
+        <v>122842182</v>
       </c>
       <c r="B6" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>361349</v>
+        <v>361303</v>
       </c>
       <c r="R6" t="n">
-        <v>6631211</v>
+        <v>6631185</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122842019</v>
+        <v>122842508</v>
       </c>
       <c r="B7" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1320,13 +1320,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>361324</v>
+        <v>361294</v>
       </c>
       <c r="R7" t="n">
-        <v>6631171</v>
+        <v>6631130</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122842182</v>
+        <v>122841777</v>
       </c>
       <c r="B8" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1441,13 +1441,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>361303</v>
+        <v>361311</v>
       </c>
       <c r="R8" t="n">
-        <v>6631185</v>
+        <v>6631219</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,7 +1516,7 @@
         <v>122841555</v>
       </c>
       <c r="B9" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122840608</v>
+        <v>122841777</v>
       </c>
       <c r="B2" t="n">
         <v>98365</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>361349</v>
+        <v>361311</v>
       </c>
       <c r="R2" t="n">
-        <v>6631211</v>
+        <v>6631219</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122840408</v>
+        <v>122841433</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -829,20 +829,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>361347</v>
+        <v>361325</v>
       </c>
       <c r="R3" t="n">
-        <v>6631224</v>
+        <v>6631198</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122841433</v>
+        <v>122842508</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -943,7 +952,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>361325</v>
+        <v>361294</v>
       </c>
       <c r="R4" t="n">
-        <v>6631198</v>
+        <v>6631130</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122842019</v>
+        <v>122841555</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1064,7 +1073,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1078,13 +1087,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>361324</v>
+        <v>361315</v>
       </c>
       <c r="R5" t="n">
-        <v>6631171</v>
+        <v>6631258</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,7 +1159,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122842182</v>
+        <v>122842019</v>
       </c>
       <c r="B6" t="n">
         <v>98365</v>
@@ -1185,7 +1194,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1199,13 +1208,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>361303</v>
+        <v>361324</v>
       </c>
       <c r="R6" t="n">
-        <v>6631185</v>
+        <v>6631171</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122842508</v>
+        <v>122842182</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1306,7 +1315,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1320,10 +1329,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>361294</v>
+        <v>361303</v>
       </c>
       <c r="R7" t="n">
-        <v>6631130</v>
+        <v>6631185</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1364,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1374,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,7 +1401,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122841777</v>
+        <v>122840738</v>
       </c>
       <c r="B8" t="n">
         <v>98365</v>
@@ -1427,7 +1436,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1441,10 +1450,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>361311</v>
+        <v>361349</v>
       </c>
       <c r="R8" t="n">
-        <v>6631219</v>
+        <v>6631211</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1476,7 +1485,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1495,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,7 +1522,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122841555</v>
+        <v>122840408</v>
       </c>
       <c r="B9" t="n">
         <v>98365</v>
@@ -1546,29 +1555,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>361315</v>
+        <v>361347</v>
       </c>
       <c r="R9" t="n">
-        <v>6631258</v>
+        <v>6631224</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -1401,7 +1401,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122840738</v>
+        <v>122840408</v>
       </c>
       <c r="B8" t="n">
         <v>98365</v>
@@ -1434,26 +1434,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>361349</v>
+        <v>361347</v>
       </c>
       <c r="R8" t="n">
-        <v>6631211</v>
+        <v>6631224</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1485,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1495,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,7 +1513,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122840408</v>
+        <v>122840738</v>
       </c>
       <c r="B9" t="n">
         <v>98365</v>
@@ -1555,17 +1546,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>361347</v>
+        <v>361349</v>
       </c>
       <c r="R9" t="n">
-        <v>6631224</v>
+        <v>6631211</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122841777</v>
+        <v>122840608</v>
       </c>
       <c r="B2" t="n">
         <v>98365</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>361311</v>
+        <v>361349</v>
       </c>
       <c r="R2" t="n">
-        <v>6631219</v>
+        <v>6631211</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122841433</v>
+        <v>122842508</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>361325</v>
+        <v>361294</v>
       </c>
       <c r="R3" t="n">
-        <v>6631198</v>
+        <v>6631130</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122842508</v>
+        <v>122841433</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -952,7 +952,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>361294</v>
+        <v>361325</v>
       </c>
       <c r="R4" t="n">
-        <v>6631130</v>
+        <v>6631198</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122841555</v>
+        <v>122841777</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>361315</v>
+        <v>361311</v>
       </c>
       <c r="R5" t="n">
-        <v>6631258</v>
+        <v>6631219</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1159,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122842019</v>
+        <v>122840408</v>
       </c>
       <c r="B6" t="n">
         <v>98365</v>
@@ -1192,26 +1192,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>361324</v>
+        <v>361347</v>
       </c>
       <c r="R6" t="n">
-        <v>6631171</v>
+        <v>6631224</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1243,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,7 +1271,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122842182</v>
+        <v>122841555</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1315,7 +1306,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1329,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>361303</v>
+        <v>361315</v>
       </c>
       <c r="R7" t="n">
-        <v>6631185</v>
+        <v>6631258</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1374,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,7 +1392,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122840408</v>
+        <v>122842019</v>
       </c>
       <c r="B8" t="n">
         <v>98365</v>
@@ -1434,17 +1425,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>361347</v>
+        <v>361324</v>
       </c>
       <c r="R8" t="n">
-        <v>6631224</v>
+        <v>6631171</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,7 +1513,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122840738</v>
+        <v>122842182</v>
       </c>
       <c r="B9" t="n">
         <v>98365</v>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1562,13 +1562,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>361349</v>
+        <v>361303</v>
       </c>
       <c r="R9" t="n">
-        <v>6631211</v>
+        <v>6631185</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122840608</v>
+        <v>122842019</v>
       </c>
       <c r="B2" t="n">
         <v>98365</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>361349</v>
+        <v>361324</v>
       </c>
       <c r="R2" t="n">
-        <v>6631211</v>
+        <v>6631171</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122841433</v>
+        <v>122840408</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -950,29 +950,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>361325</v>
+        <v>361347</v>
       </c>
       <c r="R4" t="n">
-        <v>6631198</v>
+        <v>6631224</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122841777</v>
+        <v>122841433</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1073,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,13 +1078,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>361311</v>
+        <v>361325</v>
       </c>
       <c r="R5" t="n">
-        <v>6631219</v>
+        <v>6631198</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1150,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122840408</v>
+        <v>122840608</v>
       </c>
       <c r="B6" t="n">
         <v>98365</v>
@@ -1192,17 +1183,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>361347</v>
+        <v>361349</v>
       </c>
       <c r="R6" t="n">
-        <v>6631224</v>
+        <v>6631211</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,7 +1271,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122841555</v>
+        <v>122841777</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1320,13 +1320,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>361315</v>
+        <v>361311</v>
       </c>
       <c r="R7" t="n">
-        <v>6631258</v>
+        <v>6631219</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,7 +1392,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122842019</v>
+        <v>122841555</v>
       </c>
       <c r="B8" t="n">
         <v>98365</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1441,13 +1441,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>361324</v>
+        <v>361315</v>
       </c>
       <c r="R8" t="n">
-        <v>6631171</v>
+        <v>6631258</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122842019</v>
+        <v>122841433</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>361324</v>
+        <v>361325</v>
       </c>
       <c r="R2" t="n">
-        <v>6631171</v>
+        <v>6631198</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122842508</v>
+        <v>122840408</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,29 +829,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>361294</v>
+        <v>361347</v>
       </c>
       <c r="R3" t="n">
-        <v>6631130</v>
+        <v>6631224</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122840408</v>
+        <v>122840738</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,17 +941,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>361347</v>
+        <v>361349</v>
       </c>
       <c r="R4" t="n">
-        <v>6631224</v>
+        <v>6631211</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122841433</v>
+        <v>122842182</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>361325</v>
+        <v>361303</v>
       </c>
       <c r="R5" t="n">
-        <v>6631198</v>
+        <v>6631185</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122840608</v>
+        <v>122842508</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>361349</v>
+        <v>361294</v>
       </c>
       <c r="R6" t="n">
-        <v>6631211</v>
+        <v>6631130</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,7 +1274,7 @@
         <v>122841777</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>122841555</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122842182</v>
+        <v>122842019</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1562,13 +1562,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>361303</v>
+        <v>361324</v>
       </c>
       <c r="R9" t="n">
-        <v>6631185</v>
+        <v>6631171</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122841433</v>
+        <v>122840408</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,29 +708,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>361325</v>
+        <v>361347</v>
       </c>
       <c r="R2" t="n">
-        <v>6631198</v>
+        <v>6631224</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122840408</v>
+        <v>122841433</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,20 +820,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>361347</v>
+        <v>361325</v>
       </c>
       <c r="R3" t="n">
-        <v>6631224</v>
+        <v>6631198</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122840738</v>
+        <v>122840608</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122842182</v>
+        <v>122842508</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>361303</v>
+        <v>361294</v>
       </c>
       <c r="R5" t="n">
-        <v>6631185</v>
+        <v>6631130</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122842508</v>
+        <v>122842019</v>
       </c>
       <c r="B6" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>361294</v>
+        <v>361324</v>
       </c>
       <c r="R6" t="n">
-        <v>6631130</v>
+        <v>6631171</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122841777</v>
+        <v>122842182</v>
       </c>
       <c r="B7" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1320,13 +1320,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>361311</v>
+        <v>361303</v>
       </c>
       <c r="R7" t="n">
-        <v>6631219</v>
+        <v>6631185</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122841555</v>
+        <v>122841777</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1441,13 +1441,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>361315</v>
+        <v>361311</v>
       </c>
       <c r="R8" t="n">
-        <v>6631258</v>
+        <v>6631219</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,10 +1513,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122842019</v>
+        <v>122841555</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1562,13 +1562,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>361324</v>
+        <v>361315</v>
       </c>
       <c r="R9" t="n">
-        <v>6631171</v>
+        <v>6631258</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122840408</v>
+        <v>122841433</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,20 +708,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>361347</v>
+        <v>361325</v>
       </c>
       <c r="R2" t="n">
-        <v>6631224</v>
+        <v>6631198</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122841433</v>
+        <v>122841555</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>361325</v>
+        <v>361315</v>
       </c>
       <c r="R3" t="n">
-        <v>6631198</v>
+        <v>6631258</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,7 +920,7 @@
         <v>122840608</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1032,7 +1041,7 @@
         <v>122842508</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1150,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122842019</v>
+        <v>122840408</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,26 +1192,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>361324</v>
+        <v>361347</v>
       </c>
       <c r="R6" t="n">
-        <v>6631171</v>
+        <v>6631224</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,7 +1274,7 @@
         <v>122842182</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>122841777</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122841555</v>
+        <v>122842019</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1562,13 +1562,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>361315</v>
+        <v>361324</v>
       </c>
       <c r="R9" t="n">
-        <v>6631258</v>
+        <v>6631171</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1632,6 +1632,126 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129895247</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98785</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Juvasmyrenm O om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>361325</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6631199</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>S-Arv-0893</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>10 dellokaler med  19 - 94 skott i området mellan myren ocj sjöstranden.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -1637,7 +1637,7 @@
         <v>129895247</v>
       </c>
       <c r="B10" t="n">
-        <v>98785</v>
+        <v>98790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -1637,7 +1637,7 @@
         <v>129895247</v>
       </c>
       <c r="B10" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -1637,7 +1637,7 @@
         <v>129895247</v>
       </c>
       <c r="B10" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -1637,7 +1637,7 @@
         <v>129895247</v>
       </c>
       <c r="B10" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -1637,7 +1637,7 @@
         <v>129895247</v>
       </c>
       <c r="B10" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -1637,7 +1637,7 @@
         <v>129895247</v>
       </c>
       <c r="B10" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -1637,7 +1637,7 @@
         <v>129895247</v>
       </c>
       <c r="B10" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -1637,7 +1637,7 @@
         <v>129895247</v>
       </c>
       <c r="B10" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6966-2025 artfynd.xlsx
+++ b/artfynd/A 6966-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122841433</v>
+        <v>122840408</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,29 +703,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>361325</v>
+        <v>361347</v>
       </c>
       <c r="R2" t="n">
-        <v>6631198</v>
+        <v>6631224</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122842019</v>
+        <v>122840608</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>361324</v>
+        <v>361349</v>
       </c>
       <c r="R3" t="n">
-        <v>6631171</v>
+        <v>6631211</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -880,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122840608</v>
+        <v>122841433</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,7 +928,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -966,13 +942,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>361349</v>
+        <v>361325</v>
       </c>
       <c r="R4" t="n">
-        <v>6631211</v>
+        <v>6631198</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122842508</v>
+        <v>122841555</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,7 +1044,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>361294</v>
+        <v>361315</v>
       </c>
       <c r="R5" t="n">
-        <v>6631130</v>
+        <v>6631258</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,12 +1133,7 @@
         <v>122841777</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,15 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122840408</v>
+        <v>122842019</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,17 +1274,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>361347</v>
+        <v>361324</v>
       </c>
       <c r="R7" t="n">
-        <v>6631224</v>
+        <v>6631171</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1355,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,15 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122841555</v>
+        <v>122842182</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1392,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1441,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>361315</v>
+        <v>361303</v>
       </c>
       <c r="R8" t="n">
-        <v>6631258</v>
+        <v>6631185</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,15 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122842182</v>
+        <v>122842265</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1508,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1562,13 +1522,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>361303</v>
+        <v>361271</v>
       </c>
       <c r="R9" t="n">
-        <v>6631185</v>
+        <v>6631198</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1597,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1634,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129895247</v>
+        <v>122842508</v>
       </c>
       <c r="B10" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,24 +1624,24 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Juvasmyrenm O om, Vrm</t>
+          <t>Juvasmyren, Juvasmyren, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>361325</v>
+        <v>361294</v>
       </c>
       <c r="R10" t="n">
-        <v>6631199</v>
+        <v>6631130</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,24 +1666,24 @@
           <t>Gunnarskog</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>S-Arv-0893</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>10 dellokaler med  19 - 94 skott i området mellan myren ocj sjöstranden.</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,19 +1698,357 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127493492</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Juvasen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>361340</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6631125</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Arne Holgersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Arne Holgersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129895247</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Juvasmyrenm O om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>361325</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6631199</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>S-Arv-0893</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>10 dellokaler med  19 - 94 skott i området mellan myren ocj sjöstranden.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Owe Nilsson</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Petrus Oledal</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127493493</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Juvasen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>361340</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6631125</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Arne Holgersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Arne Holgersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
